--- a/Registro_De_Terrenos_Municipal.xlsx
+++ b/Registro_De_Terrenos_Municipal.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC2E351-4C49-4433-B647-B2B1578A0391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0620FD10-A260-4E9D-A0BE-90590C0F4149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Registro de Terrenos" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="182">
   <si>
     <t>SISTEMA UNIFICADO DE REGISTRO CATASTRAL DE TERRENOS MUNICIPALES</t>
   </si>
@@ -556,6 +556,18 @@
   </si>
   <si>
     <t>Recaudación Impuesto Anual Estimada ($)</t>
+  </si>
+  <si>
+    <t>Lic Julice Cruz</t>
+  </si>
+  <si>
+    <t>Analista</t>
+  </si>
+  <si>
+    <t>JUL-6969-KEY</t>
+  </si>
+  <si>
+    <t>USR-CAT-05</t>
   </si>
 </sst>
 </file>
@@ -2253,7 +2265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -2382,6 +2394,26 @@
       </c>
       <c r="F7" s="20" t="s">
         <v>168</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
